--- a/site/public/DwellingDamageProfile-definition.xlsx
+++ b/site/public/DwellingDamageProfile-definition.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>9 fields defined</t>
+          <t>26 fields defined</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -754,66 +754,58 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>damage_level</t>
+          <t>identifiers</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>concept:Identifier</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Severity of physical damage to the assessed dwelling, observed during a post-shock structural assessment. Recorded against a standardized five-tier scale aligned with IOM Displacement Tracking Matrix labels.</t>
+          <t>Identifiers carried by this entity, such as national ID numbers, program IDs, or identifiers asserted by an identity document.</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Gravité des dommages physiques au logement évalué, observée lors d'une évaluation structurelle post-choc. Consignée selon une échelle standardisée à cinq niveaux alignée sur les libellés de la Displacement Tracking Matrix de l'OIM.</t>
+          <t>Identifiants portés par cette entité, tels que numéros d'identité nationale, identifiants de programme ou identifiants attestés par un document d'identité.</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Gravedad de los daños físicos a la vivienda evaluada, observada durante una evaluación estructural post-choque. Registrada en una escala estandarizada de cinco niveles alineada con las etiquetas de la Matriz de Seguimiento del Desplazamiento de la OIM.</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>shelter-damage-level</t>
-        </is>
-      </c>
+          <t>Identificadores que porta esta entidad, como números de identidad nacional, ID de programa o identificadores acreditados por un documento de identidad.</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>normative</t>
         </is>
       </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>shelter</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>habitability_status</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>concept:Party</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -823,51 +815,39 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Programming-facing judgement of whether the assessed dwelling can currently be occupied and what category of shelter response it requires. Distinct from damage_level: a moderately damaged structure may still be habitable, and a lightly damaged one may be vacated for other reasons.</t>
+          <t>The person or group that the profile or scoring event is about. Ranged at Party (not Agent) because Profiles observe receivers: persons and organised groups of persons (Household, Family, Farm). Institutional actors (Organizations) are described through their own Organization records, not as subjects of a Profile.</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Jugement orienté programmation sur l'occupabilité actuelle du logement évalué et la catégorie de réponse abri requise. Distinct de damage_level : une structure modérément endommagée peut rester habitable, et une structure légèrement endommagée peut être abandonnée pour d'autres raisons.</t>
+          <t>La personne ou le groupe sur lequel porte le profil ou l'événement de notation. Typé sur Party (et non Agent) parce que les Profiles observent des bénéficiaires : personnes et groupes organisés de personnes (Household, Family, Farm). Les acteurs institutionnels (Organizations) sont décrits par leurs propres enregistrements Organization, non comme sujets d'un Profile.</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Juicio orientado a la programación sobre si la vivienda evaluada puede ocuparse actualmente y qué categoría de respuesta de refugio requiere. Distinto de damage_level: una estructura moderadamente dañada puede seguir siendo habitable, y una ligeramente dañada puede estar desocupada por otras razones.</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>habitability-status</t>
-        </is>
-      </c>
+          <t>La persona o grupo sobre el que trata el perfil o evento de puntuación. Tipado como Party (no Agent) porque los Profile observan receptores: personas y grupos organizados de personas (Household, Family, Farm). Los actores institucionales (Organizations) se describen mediante sus propios registros Organization, no como sujetos de un Profile.</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr"/>
       <c r="H3" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>habitability</t>
-        </is>
-      </c>
+      <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>shelter_cluster_rna, reach_msna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>current_shelter_type</t>
+          <t>observation_date</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -877,55 +857,39 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Type of shelter arrangement the household is currently occupying at the time of assessment. Complements dwelling_type (which records the household's usual dwelling) by recording where the household is actually living now, particularly when the original dwelling is damaged, inaccessible, or vacated.</t>
+          <t>The date on which the profile data was collected (when the instrument was administered or the measurement taken).</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Type d'arrangement d'abri actuellement occupé par le ménage au moment de l'évaluation. Complète dwelling_type (qui consigne le logement habituel du ménage) en consignant où le ménage vit réellement maintenant, particulièrement lorsque le logement d'origine est endommagé, inaccessible ou quitté.</t>
+          <t>La date à laquelle les données du profil ont été collectées (date d'administration de l'instrument ou de prise de mesure).</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Tipo de arreglo de refugio que el hogar ocupa actualmente al momento de la evaluación. Complementa dwelling_type (que registra la vivienda habitual del hogar) al registrar dónde vive realmente el hogar ahora, particularmente cuando la vivienda original está dañada, inaccesible o desocupada.</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>shelter-situation-type</t>
-        </is>
-      </c>
+          <t>La fecha en que se recopilaron los datos del perfil (fecha en que se administró el instrumento o se tomó la medición).</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>habitability</t>
-        </is>
-      </c>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>structural_safety_assessment</t>
+          <t>performed_by</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>concept:Agent</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -935,105 +899,81 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Optional structural safety tag assigned by a qualified engineer or trained shelter assessor, using the ATC-20 green/yellow/red taxonomy. Frequently null: a household enumerator is not expected to assign a structural safety tag, and many post-shock administrations do not include a structural inspector visit.</t>
+          <t>The agent (enumerator, field officer, or agency) accountable for administering the instrument or taking the measurement. Typically a Person or an Organization. When a software tool captured or derived the data, record it separately as software_used; performed_by identifies who is responsible, not what ran the capture.</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Étiquette de sécurité structurale optionnelle attribuée par un ingénieur qualifié ou un évaluateur abri formé, selon la taxonomie ATC-20 vert/jaune/rouge. Souvent nulle : un enquêteur de ménage n'est pas censé attribuer une étiquette de sécurité structurale, et de nombreuses administrations post-choc ne comportent pas de visite d'inspecteur structurel.</t>
+          <t>L'agent (enquêteur, agent de terrain ou organisme) responsable de l'administration de l'instrument ou de la prise de mesure. Généralement une Person ou une Organization. Lorsqu'un outil logiciel a capturé ou dérivé les données, enregistrez-le séparément via software_used ; performed_by identifie qui est responsable, et non ce qui a réalisé la capture.</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Etiqueta opcional de seguridad estructural asignada por un ingeniero calificado o evaluador de refugio capacitado, usando la taxonomía ATC-20 verde/amarillo/rojo. Frecuentemente nula: un encuestador del hogar no se espera que asigne una etiqueta de seguridad estructural, y muchas administraciones post-choque no incluyen una visita de inspector estructural.</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>structural-safety-tag</t>
-        </is>
-      </c>
+          <t>El agente (encuestador, agente de campo u organismo) responsable de administrar el instrumento o tomar la medición. Normalmente una Person o una Organization. Cuando una herramienta de software capturó o derivó los datos, regístrelo por separado mediante software_used; performed_by identifica quién es responsable, no qué ejecutó la captura.</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
       <c r="H5" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>shelter</t>
-        </is>
-      </c>
+      <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>shelter_cluster_rna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>essential_items_missing</t>
+          <t>instrument_used</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>concept:Instrument</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>single</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Categories of non-food items the household currently lacks and would need to meet minimum shelter and settlement standards. Multi-select across the Sphere 2018 minimum NFI package.</t>
+          <t>Reference to the instrument (survey form, questionnaire, screening protocol, measurement procedure) administered in this profile record.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Catégories d'articles non alimentaires manquant actuellement au ménage et nécessaires pour répondre aux normes minimales d'abri et d'établissement. Sélection multiple sur le paquet NFI minimum Sphère 2018.</t>
+          <t>Référence à l'instrument (formulaire d'enquête, questionnaire, protocole de dépistage, procédure de mesure) administré dans cet enregistrement de profil.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Categorías de artículos no alimentarios que el hogar carece actualmente y necesitaría para cumplir con los estándares mínimos de refugio y asentamiento. Selección múltiple sobre el paquete NFI mínimo Esfera 2018.</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>nfi-item-type</t>
-        </is>
-      </c>
+          <t>Referencia al instrumento (formulario de encuesta, cuestionario, protocolo de detección, procedimiento de medición) administrado en este registro de perfil.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>nfi</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>reconstruction_intent</t>
+          <t>software_used</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>concept:SoftwareAgent</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1043,46 +983,34 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>The household's stated intent regarding the damaged dwelling: repair in place, rebuild in place, relocate, unable to act without external support, or undecided. Used by recovery programming to target repair grants, reconstruction grants, and relocation assistance.</t>
+          <t>The software that performed this step, recorded so the result can be reproduced or audited. Distinct from the accountable evaluator or performer (the person or organisation responsible), which is recorded separately.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Intention déclarée du ménage concernant le logement endommagé : réparer sur place, reconstruire sur place, se relocaliser, incapable d'agir sans soutien extérieur, ou indécis. Utilisé par la programmation de relèvement pour cibler les subventions de réparation, les subventions de reconstruction et l'assistance à la relocalisation.</t>
+          <t>Le logiciel qui a effectué cette étape, enregistré afin que le résultat puisse être reproduit ou audité. Distinct de l'évaluateur ou de l'exécutant responsable (la personne ou l'organisme qui en répond), enregistré séparément.</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Intención declarada del hogar respecto a la vivienda dañada: reparar en el mismo sitio, reconstruir en el mismo sitio, relocalizarse, no puede actuar sin apoyo externo, o indeciso. Usado por la programación de recuperación para focalizar subvenciones de reparación, subvenciones de reconstrucción y asistencia de relocalización.</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>reconstruction-intent</t>
-        </is>
-      </c>
+          <t>El software que ejecutó este paso, registrado para que el resultado pueda reproducirse o auditarse. Distinto del evaluador o ejecutor responsable (la persona u organismo que responde), que se registra por separado.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>recovery</t>
-        </is>
-      </c>
+      <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>iom_dtm_household, pdna_housing, reach_msna</t>
-        </is>
-      </c>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>services_disrupted</t>
+          <t>administration_mode</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1092,27 +1020,27 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>single</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Essential services (water, sanitation, electricity, telecommunications) that are currently degraded at the household's dwelling after the shock. Multi-select. Codes cover both full outage and partial-function cases: water may be absent, intermittent, or present-but-unsafe; sanitation may be unusable or present-but-overflowing; electricity may be absent or intermittent. Distinct from the household's baseline service infrastructure type, which is recorded by water_source, sanitation_facility, and electricity_access.</t>
+          <t>How the instrument was administered to the subject: self-report, proxy-report (someone else answering about the subject), assisted (the subject answering with help), or mixed. Washington Group analytical guidance recommends disaggregating prevalence by administration mode because proxy responses systematically underreport difficulty.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Services essentiels (eau, assainissement, électricité, télécommunications) actuellement dégradés au logement du ménage après le choc. Sélection multiple. Les codes couvrent à la fois la coupure complète et les cas de fonctionnement partiel : l'eau peut être absente, intermittente ou présente mais non potable ; l'assainissement peut être inutilisable ou présent mais débordant ; l'électricité peut être absente ou intermittente. Distinct du type d'infrastructure de service habituel du ménage, consigné par water_source, sanitation_facility et electricity_access.</t>
+          <t>Comment l'instrument a été administré au sujet : auto-déclaration, déclaration par procuration (quelqu'un d'autre répondant au sujet du sujet), assisté (le sujet répondant avec aide) ou mixte. Les lignes directrices analytiques du Washington Group recommandent de désagréger la prévalence par mode d'administration, car les réponses par procuration sous-déclarent systématiquement la difficulté.</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Servicios esenciales (agua, saneamiento, electricidad, telecomunicaciones) que actualmente están degradados en la vivienda del hogar después del choque. Selección múltiple. Los códigos cubren tanto el corte total como los casos de función parcial: el agua puede estar ausente, intermitente o presente pero no apta; el saneamiento puede ser inutilizable o estar presente pero desbordándose; la electricidad puede estar ausente o intermitente. Distinto del tipo de infraestructura de servicio habitual del hogar, registrado por water_source, sanitation_facility y electricity_access.</t>
+          <t>Cómo se administró el instrumento al sujeto: autoinforme, informe por terceros (otra persona responde sobre el sujeto), asistido (el sujeto responde con ayuda) o mixto. Las directrices analíticas del Washington Group recomiendan desagregar la prevalencia por modo de administración, ya que las respuestas por terceros subestiman sistemáticamente la dificultad.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>service-disruption-type</t>
+          <t>administration-mode</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1121,27 +1049,19 @@
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>wash</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>iasc_mira, iom_dtm_household, reach_msna</t>
-        </is>
-      </c>
+      <c r="L8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>triggering_hazard_event</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>concept:HazardEvent</t>
+          <t>concept:Person</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1151,17 +1071,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>The hazard event that triggered this record. On DwellingDamageProfile the referenced HazardEvent identifies the flood, earthquake, cyclone, drought, conflict event, or other shock the post-shock assessment is responding to. A record may omit this property when the damage is chronic or not attributable to a single event.</t>
+          <t>The person who provided the answers to the instrument, when different from the subject. Required whenever the administration mode is proxy or assisted.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>L'événement dangereux qui a déclenché cet enregistrement. Sur DwellingDamageProfile, le HazardEvent référencé identifie l'inondation, le séisme, le cyclone, la sécheresse, l'événement de conflit ou autre choc auquel répond l'évaluation post-choc. Un enregistrement peut omettre cette propriété lorsque les dommages sont chroniques ou non attribuables à un événement unique.</t>
+          <t>La personne qui a fourni les réponses à l'instrument, lorsqu'elle est différente du sujet. Requise lorsque le mode d'administration est par procuration ou assisté.</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>El evento de peligro que desencadenó este registro. En DwellingDamageProfile, el HazardEvent referenciado identifica la inundación, sismo, ciclón, sequía, evento de conflicto u otro choque al que responde la evaluación post-choque. Un registro puede omitir esta propiedad cuando el daño es crónico o no atribuible a un único evento.</t>
+          <t>La persona que proporcionó las respuestas al instrumento, cuando es distinta del sujeto. Requerida cuando el modo de administración es por terceros o asistido.</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -1170,72 +1090,930 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>hazard_event</t>
-        </is>
-      </c>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
-        </is>
-      </c>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>respondent_relationship</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>The relationship of the respondent to the subject (parent, spouse, guardian, caregiver, etc.). Uses relationship-type because it describes a person-to-person relationship, not a role within a group. Required whenever the administration mode is proxy or assisted.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>La relation du répondant avec le sujet (parent, conjoint, tuteur, aidant, etc.). Utilise relationship-type parce qu'elle décrit une relation entre deux personnes, et non un rôle au sein d'un groupe. Requise lorsque le mode d'administration est par procuration ou assisté.</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>La relación del respondiente con el sujeto (padre o madre, cónyuge, tutor, cuidador, etc.). Usa relationship-type porque describe una relación entre personas, no un rol dentro de un grupo. Requerida cuando el modo de administración es por terceros o asistido.</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>relationship-type</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>items_asked</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>The PublicSchema property IDs that were actually asked during this administration. Lets adopters distinguish items that were asked and declined (answer absent) from items that were not asked at all. When omitted, the item set is assumed to be the default item_set of the instrument used. The intended producer is the form compiler or collection server, which populates this list from the form definition at submission time.</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Les identifiants de propriétés PublicSchema effectivement posées lors de cette administration. Permet aux adopteurs de distinguer les items posés et refusés (réponse absente) des items qui n'ont pas été posés du tout. En l'absence de cette liste, l'ensemble d'items est présumé correspondre à l'item_set par défaut de l'instrument utilisé. Le producteur prévu est le compilateur de formulaire ou le serveur de collecte, qui remplit cette liste à partir de la définition du formulaire au moment de la soumission.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Los identificadores de propiedades PublicSchema realmente preguntados durante esta administración. Permite a los adoptantes distinguir ítems preguntados y rechazados (respuesta ausente) de ítems que no fueron preguntados. Cuando se omite, el conjunto de ítems se asume igual al item_set por defecto del instrumento utilizado. El productor previsto es el compilador de formularios o el servidor de recolección, que completa esta lista a partir de la definición del formulario al momento del envío.</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>dwelling_type</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>The type of dwelling occupied by the household (e.g., permanent structure, temporary shelter, shared housing).</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Le type de logement occupé par le ménage (par exemple, structure permanente, abri temporaire, logement partagé).</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>El tipo de vivienda ocupada por el hogar (por ejemplo, estructura permanente, refugio temporal, vivienda compartida).</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>dwelling-type</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>floor_material</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>The primary material of the floor in the household's dwelling.</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Le matériau principal du sol dans le logement du ménage.</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>El material principal del piso en la vivienda del hogar.</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>floor-material</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>wall_material</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>The primary material of the exterior walls in the household's dwelling.</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Le matériau principal des murs extérieurs dans le logement du ménage.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>El material principal de las paredes exteriores en la vivienda del hogar.</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>wall-material</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>roof_material</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>The primary material of the roof in the household's dwelling.</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Le matériau principal du toit dans le logement du ménage.</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>El material principal del techo en la vivienda del hogar.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>roof-material</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>water_source</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>The main source of drinking water used by the household.</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>La principale source d'eau potable utilisée par le ménage.</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>La principal fuente de agua potable utilizada por el hogar.</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>water-source</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>sanitation_facility</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>The type of toilet or sanitation facility used by the household.</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Le type de toilettes ou d'installation sanitaire utilisé par le ménage.</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>El tipo de instalación sanitaria o letrina utilizada por el hogar.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>sanitation-facility</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>electricity_access</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Whether the household has access to electricity from any source.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Si le ménage a accès à l'électricité, quelle qu'en soit la source.</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Si el hogar tiene acceso a electricidad de cualquier fuente.</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>damage_level</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Severity of physical damage to the assessed dwelling, observed during a post-shock structural assessment. Recorded against a standardized five-tier scale aligned with IOM Displacement Tracking Matrix labels.</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Gravité des dommages physiques au logement évalué, observée lors d'une évaluation structurelle post-choc. Consignée selon une échelle standardisée à cinq niveaux alignée sur les libellés de la Displacement Tracking Matrix de l'OIM.</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Gravedad de los daños físicos a la vivienda evaluada, observada durante una evaluación estructural post-choque. Registrada en una escala estandarizada de cinco niveles alineada con las etiquetas de la Matriz de Seguimiento del Desplazamiento de la OIM.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>shelter-damage-level</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>habitability_status</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Programming-facing judgement of whether the assessed dwelling can currently be occupied and what category of shelter response it requires. Distinct from damage_level: a moderately damaged structure may still be habitable, and a lightly damaged one may be vacated for other reasons.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Jugement orienté programmation sur l'occupabilité actuelle du logement évalué et la catégorie de réponse abri requise. Distinct de damage_level : une structure modérément endommagée peut rester habitable, et une structure légèrement endommagée peut être abandonnée pour d'autres raisons.</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Juicio orientado a la programación sobre si la vivienda evaluada puede ocuparse actualmente y qué categoría de respuesta de refugio requiere. Distinto de damage_level: una estructura moderadamente dañada puede seguir siendo habitable, y una ligeramente dañada puede estar desocupada por otras razones.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>habitability-status</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>habitability</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>shelter_cluster_rna, reach_msna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>current_shelter_type</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Type of shelter arrangement the household is currently occupying at the time of assessment. Complements dwelling_type (which records the household's usual dwelling) by recording where the household is actually living now, particularly when the original dwelling is damaged, inaccessible, or vacated.</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Type d'arrangement d'abri actuellement occupé par le ménage au moment de l'évaluation. Complète dwelling_type (qui consigne le logement habituel du ménage) en consignant où le ménage vit réellement maintenant, particulièrement lorsque le logement d'origine est endommagé, inaccessible ou quitté.</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Tipo de arreglo de refugio que el hogar ocupa actualmente al momento de la evaluación. Complementa dwelling_type (que registra la vivienda habitual del hogar) al registrar dónde vive realmente el hogar ahora, particularmente cuando la vivienda original está dañada, inaccesible o desocupada.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>shelter-situation-type</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>habitability</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>structural_safety_assessment</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Optional structural safety tag assigned by a qualified engineer or trained shelter assessor, using the ATC-20 green/yellow/red taxonomy. Frequently null: a household enumerator is not expected to assign a structural safety tag, and many post-shock administrations do not include a structural inspector visit.</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Étiquette de sécurité structurale optionnelle attribuée par un ingénieur qualifié ou un évaluateur abri formé, selon la taxonomie ATC-20 vert/jaune/rouge. Souvent nulle : un enquêteur de ménage n'est pas censé attribuer une étiquette de sécurité structurale, et de nombreuses administrations post-choc ne comportent pas de visite d'inspecteur structurel.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Etiqueta opcional de seguridad estructural asignada por un ingeniero calificado o evaluador de refugio capacitado, usando la taxonomía ATC-20 verde/amarillo/rojo. Frecuentemente nula: un encuestador del hogar no se espera que asigne una etiqueta de seguridad estructural, y muchas administraciones post-choque no incluyen una visita de inspector estructural.</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>structural-safety-tag</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>shelter_cluster_rna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>essential_items_missing</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Categories of non-food items the household currently lacks and would need to meet minimum shelter and settlement standards. Multi-select across the Sphere 2018 minimum NFI package.</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Catégories d'articles non alimentaires manquant actuellement au ménage et nécessaires pour répondre aux normes minimales d'abri et d'établissement. Sélection multiple sur le paquet NFI minimum Sphère 2018.</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Categorías de artículos no alimentarios que el hogar carece actualmente y necesitaría para cumplir con los estándares mínimos de refugio y asentamiento. Selección múltiple sobre el paquete NFI mínimo Esfera 2018.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>nfi-item-type</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>nfi</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>reconstruction_intent</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>The household's stated intent regarding the damaged dwelling: repair in place, rebuild in place, relocate, unable to act without external support, or undecided. Used by recovery programming to target repair grants, reconstruction grants, and relocation assistance.</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Intention déclarée du ménage concernant le logement endommagé : réparer sur place, reconstruire sur place, se relocaliser, incapable d'agir sans soutien extérieur, ou indécis. Utilisé par la programmation de relèvement pour cibler les subventions de réparation, les subventions de reconstruction et l'assistance à la relocalisation.</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Intención declarada del hogar respecto a la vivienda dañada: reparar en el mismo sitio, reconstruir en el mismo sitio, relocalizarse, no puede actuar sin apoyo externo, o indeciso. Usado por la programación de recuperación para focalizar subvenciones de reparación, subvenciones de reconstrucción y asistencia de relocalización.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>reconstruction-intent</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>iom_dtm_household, pdna_housing, reach_msna</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>services_disrupted</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Essential services (water, sanitation, electricity, telecommunications) that are currently degraded at the household's dwelling after the shock. Multi-select. Codes cover both full outage and partial-function cases: water may be absent, intermittent, or present-but-unsafe; sanitation may be unusable or present-but-overflowing; electricity may be absent or intermittent. Distinct from the household's baseline service infrastructure type, which is recorded by water_source, sanitation_facility, and electricity_access.</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Services essentiels (eau, assainissement, électricité, télécommunications) actuellement dégradés au logement du ménage après le choc. Sélection multiple. Les codes couvrent à la fois la coupure complète et les cas de fonctionnement partiel : l'eau peut être absente, intermittente ou présente mais non potable ; l'assainissement peut être inutilisable ou présent mais débordant ; l'électricité peut être absente ou intermittente. Distinct du type d'infrastructure de service habituel du ménage, consigné par water_source, sanitation_facility et electricity_access.</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Servicios esenciales (agua, saneamiento, electricidad, telecomunicaciones) que actualmente están degradados en la vivienda del hogar después del choque. Selección múltiple. Los códigos cubren tanto el corte total como los casos de función parcial: el agua puede estar ausente, intermitente o presente pero no apta; el saneamiento puede ser inutilizable o estar presente pero desbordándose; la electricidad puede estar ausente o intermitente. Distinto del tipo de infraestructura de servicio habitual del hogar, registrado por water_source, sanitation_facility y electricity_access.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>service-disruption-type</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>iasc_mira, iom_dtm_household, reach_msna</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>triggering_hazard_event</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>concept:HazardEvent</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>The hazard event that triggered this record. On DwellingDamageProfile the referenced HazardEvent identifies the flood, earthquake, cyclone, drought, conflict event, or other shock the post-shock assessment is responding to. A record may omit this property when the damage is chronic or not attributable to a single event.</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>L'événement dangereux qui a déclenché cet enregistrement. Sur DwellingDamageProfile, le HazardEvent référencé identifie l'inondation, le séisme, le cyclone, la sécheresse, l'événement de conflit ou autre choc auquel répond l'évaluation post-choc. Un enregistrement peut omettre cette propriété lorsque les dommages sont chroniques ou non attribuables à un événement unique.</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>El evento de peligro que desencadenó este registro. En DwellingDamageProfile, el HazardEvent referenciado identifica la inundación, sismo, ciclón, sequía, evento de conflicto u otro choque al que responde la evaluación post-choque. Un registro puede omitir esta propiedad cuando el daño es crónico o no atribuible a un único evento.</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>hazard_event</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>location_of_assessment</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>concept:Location</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>The physical location where the post-shock assessment was carried out, typically the location of the assessed dwelling. Distinct from Household.location (which is the household's registered administrative or coordinate location): the two may differ if the household has displaced, relocated, or is temporarily sheltering elsewhere while the assessed structure remains at its registered site.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Emplacement physique où l'évaluation post-choc a été effectuée, typiquement l'emplacement du logement évalué. Distinct de Household.location (emplacement administratif ou géographique enregistré du ménage) : les deux peuvent différer si le ménage s'est déplacé, a été relocalisé ou s'abrite temporairement ailleurs tandis que la structure évaluée demeure sur son site enregistré.</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Ubicación física donde se realizó la evaluación post-choque, típicamente la ubicación de la vivienda evaluada. Distinta de Household.location (la ubicación administrativa o geográfica registrada del hogar): las dos pueden diferir si el hogar se ha desplazado, relocalizado o se refugia temporalmente en otro lugar mientras la estructura evaluada permanece en su sitio registrado.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>sensitive</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>iasc_mira, iom_dtm_household, shelter_cluster_rna, reach_msna, pdna_housing</t>
         </is>

--- a/site/public/DwellingDamageProfile-definition.xlsx
+++ b/site/public/DwellingDamageProfile-definition.xlsx
@@ -2396,11 +2396,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
@@ -2673,6 +2673,60 @@
       <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Household is without shelter (sleeping outside, under tarpaulin strung between trees, or in vehicles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>camp_planned</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Planned or managed camp</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Camp planifié ou géré</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Campamento planificado o gestionado</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Household is living in an official displacement camp or settlement managed by a government, UN agency, or NGO with designated administration. Equivalent to IOM DTM site classification 'planned/managed camp'. Distinct from spontaneous_settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>spontaneous_settlement</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Spontaneous or informal settlement</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Établissement spontané ou informel</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Asentamiento espontáneo o informal</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Household is living in an unplanned settlement that emerged organically, often on public or private land without official sanction or management. Equivalent to IOM DTM site classification 'informal/spontaneous settlement'.</t>
         </is>
       </c>
     </row>

--- a/site/public/DwellingDamageProfile-definition.xlsx
+++ b/site/public/DwellingDamageProfile-definition.xlsx
@@ -2870,13 +2870,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3207,25 +3207,295 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>cooking_pot</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Cooking pot</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Marmite</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Olla</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Large cooking pot with handle and lid for household meal preparation. Used in NFIProfile unmet-needs reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>plate_or_bowl</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Plate or bowl</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Assiette ou bol</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Plato o tazón</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Dished plate or deep bowl for individual meal serving (Sphere Std 2: one per person).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>cup_or_mug</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Cup or mug</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Tasse ou mug</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Taza o jarro</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Drinking vessel (Sphere Std 2: one per person).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>kitchen_knife</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen knife</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Couteau de cuisine</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Cuchillo de cocina</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Knife for food preparation (Sphere Std 2: one per household).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>matches_or_lighter</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Matches or lighter</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Allumettes ou briquet</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Fósforos o encendedor</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Ignition source for cooking stove or fire. UNHCR CRI: listed as a renewable NFI requiring regular resupply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>mosquito_net</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Mosquito net (ITN/LLIN)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Moustiquaire (MII/MIILDA)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Mosquitero (MTI/MILD)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Insecticide-treated mosquito net for sleeping protection. Sphere Std 1 key indicator in malaria-endemic settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>clothing_adult</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Clothing (adult)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Vêtements (adulte)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Ropa (adulto)</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Climate-appropriate clothing set for adult household members. Sphere Std 1: two full sets per person in the correct size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>clothing_child</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Clothing (child)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Vêtements (enfant)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Ropa (niño)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Climate-appropriate clothing set for child household members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>shelter_repair_tools</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Shelter repair tools</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Outils de réparation d'abri</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Herramientas de reparación de refugio</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Hammer, nails, rope or equivalent shelter maintenance kit (Sphere Std 4 tools and equipment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>water_jerrycan</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Water jerry can</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Jerrican à eau</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Bidón para agua</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Lidded water transport and storage container (10-20 litre). Overlaps with the generic jerrycan code; water_jerrycan is used in NFIProfile unmet-needs reporting when the specific use case is water-carrying rather than fuel storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>Otro</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Other essential NFI not captured by the standard categories; narrative description expected at the record level.</t>
         </is>

--- a/site/public/DwellingDamageProfile-definition.xlsx
+++ b/site/public/DwellingDamageProfile-definition.xlsx
@@ -9,13 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shelter-damage-level" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="habitability-status" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shelter-situation-type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="structural-safety-tag" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nfi-item-type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconstruction-intent" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="service-disruption-type" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="administration-mode" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relationship-type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dwelling-type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="floor-material" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wall-material" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="roof-material" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="water-source" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sanitation-facility" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shelter-damage-level" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="habitability-status" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shelter-situation-type" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="structural-safety-tag" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nfi-item-type" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconstruction-intent" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="service-disruption-type" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,6 +673,2361 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>flush_to_piped_sewer</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Flush to piped sewer system</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Chasse vers réseau d'égout canalisé</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Descarga a red de alcantarillado</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>A flush or pour-flush toilet connected to a municipal or communal piped sewer network.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>flush_to_septic_tank</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Flush to septic tank</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Chasse vers fosse septique</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Descarga a fosa séptica</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>A flush or pour-flush toilet connected to an on-site septic tank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>flush_to_pit_latrine</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Flush to pit latrine</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Chasse vers fosse</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Descarga a letrina de fosa</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>A flush or pour-flush toilet where waste is directed to a pit below or nearby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>flush_to_open_drain</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Flush to open drain</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Chasse vers caniveau ouvert</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Descarga a canal abierto</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>A flush or pour-flush toilet where waste is discharged into an open drain or ditch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>flush_to_unknown</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Flush to unknown place / don't know where</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Chasse vers destination inconnue / ne sait pas</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Descarga a lugar desconocido / no sabe adónde</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>A flush or pour-flush toilet where the destination of waste is unknown or the respondent does not know.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ventilated_improved_pit</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Ventilated improved pit latrine (VIP)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Latrine à fosse améliorée ventilée (VIP)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Letrina de fosa mejorada ventilada (VIP)</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>A pit latrine fitted with a ventilation pipe and a fly screen, which reduces odours and fly breeding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>pit_latrine_with_slab</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Pit latrine with slab</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Latrine à fosse avec dalle</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Letrina de fosa con losa</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>A pit latrine with a concrete or other solid slab covering the pit, reducing contamination risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>pit_latrine_without_slab</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Pit latrine without slab / open pit</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Latrine à fosse sans dalle / fosse ouverte</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Letrina de fosa sin losa / fosa abierta</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>A pit latrine with no covering slab, leaving the pit directly exposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>composting_toilet</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Composting toilet</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Toilettes à compostage</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Inodoro de compostaje</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>A dry toilet that treats human waste through aerobic decomposition, producing compost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>bucket_latrine</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Bucket latrine</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Latrine à seau</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Letrina de cubo</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>A toilet or latrine in which waste is collected in a bucket or container for later removal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>hanging_toilet</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Hanging toilet / hanging latrine</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Toilettes suspendues / latrine suspendue</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Inodoro colgante / letrina colgante</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>A toilet or latrine built over water or open ground where waste falls directly below without containment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>open_defecation</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>No facility / bush / field (open defecation)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Aucune installation / brousse / champ (défécation à l'air libre)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Sin instalación / campo / monte (defecación al aire libre)</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>No toilet or latrine is used; defecation takes place in the open, in fields, forests, bodies of water, or other open spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>A sanitation facility not covered by the other categories.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>destroyed</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Destroyed</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Détruit</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Destruido</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>The structure is completely destroyed or collapsed; rebuilding from foundation is required. Not habitable under any condition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>severely_damaged</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Severely damaged</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Gravement endommagé</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Gravemente dañado</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Major structural damage to load-bearing elements (walls, roof, foundation) rendering the dwelling unsafe. Extensive reconstruction is required before safe occupancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>moderately_damaged</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Moderately damaged</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Modérément endommagé</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Moderadamente dañado</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Significant damage to non-structural elements (walls, openings, partitions) or limited structural damage. Major repairs are required; dwelling may be temporarily uninhabitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>minor_damage</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Minor damage</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Dommages mineurs</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Daños menores</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Minor cosmetic or surface damage (cracks, finishes, fixtures). Dwelling remains habitable; minor household-level repairs are sufficient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>undamaged</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Undamaged</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Non endommagé</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Sin daños</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>No observable damage from the shock. Recorded to distinguish from missing observation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>habitable</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Dwelling is currently occupied or occupiable without intervention. No shelter programming action required from a habitability standpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>needs_minor_repairs</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Habitable with minor repairs</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Habitable avec réparations mineures</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Habitable con reparaciones menores</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Dwelling is livable now; minor household-level repairs (patching, finishes, replacing fixtures) would restore normal function. Typical response: NFI kit or small cash grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>needs_major_repairs_uninhabitable</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Uninhabitable; major repairs required (repair-grant tier)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Inhabitable ; réparations majeures requises (tranche subvention-réparation)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Inhabitable; se requieren reparaciones mayores (tramo subvención-reparación)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Dwelling cannot currently be occupied but can be repaired to a safe habitable standard without full reconstruction. Typical response: shelter repair grant, technical assistance, labour support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>must_be_demolished</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Beyond repair; must be demolished (reconstruction-grant tier)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Irréparable ; doit être démoli (tranche subvention-reconstruction)</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Irreparable; debe demolerse (tramo subvención-reconstrucción)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Dwelling is beyond safe repair and must be demolished; recovery requires full reconstruction. Typical response: transitional shelter, reconstruction grant, relocation support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Unknown / not assessed</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Inconnu / non évalué</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Desconocido / no evaluado</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Habitability has not been assessed. Recorded to distinguish from a positive 'habitable' finding.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>original_home</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Original home</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Logement d'origine</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Vivienda original</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Household remains in its usual dwelling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>original_home_repaired</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Original home, partially repaired</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Logement d'origine, partiellement réparé</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Vivienda original, parcialmente reparada</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Household is back in its usual dwelling after undertaking partial repairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>tent_or_emergency_shelter</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Tent or emergency shelter</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Tente ou abri d'urgence</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Tienda o refugio de emergencia</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Household is living in an emergency tent, plastic-sheeting shelter, or similar emergency structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>transitional_shelter</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Transitional shelter</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Abri transitionnel</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Refugio transicional</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Household is living in a transitional shelter unit provided by a humanitarian agency or government, intended as a bridge to permanent reconstruction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>collective_center</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Collective centre</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Centre collectif</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Centro colectivo</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Household is sheltering in a collective centre such as a school, public hall, or place of worship being used as temporary accommodation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>host_family</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Hosted by another family</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Hébergé par une autre famille</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Alojado por otra familia</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Household is staying with a host family (relatives, friends, or other hosts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>rented_accommodation</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Rented accommodation</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Logement loué</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Alojamiento alquilado</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Household has rented a separate dwelling as temporary or continuing accommodation after the shock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>displacement_site</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Displacement site or camp</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Site de déplacement ou camp</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Sitio de desplazamiento o campamento</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Household is in a managed displacement site or camp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>unsheltered</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Unsheltered / open air</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Sans abri / à l'air libre</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Sin refugio / a la intemperie</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Household is without shelter (sleeping outside, under tarpaulin strung between trees, or in vehicles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>camp_planned</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Planned or managed camp</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Camp planifié ou géré</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Campamento planificado o gestionado</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Household is living in an official displacement camp or settlement managed by a government, UN agency, or NGO with designated administration. Equivalent to IOM DTM site classification 'planned/managed camp'. Distinct from spontaneous_settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>spontaneous_settlement</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Spontaneous or informal settlement</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Établissement spontané ou informel</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Asentamiento espontáneo o informal</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Household is living in an unplanned settlement that emerged organically, often on public or private land without official sanction or management. Equivalent to IOM DTM site classification 'informal/spontaneous settlement'.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Safe (green tag)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Sûr (étiquette verte)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Seguro (etiqueta verde)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Building is structurally safe to occupy; no restrictions identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>restricted_use</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Restricted use (yellow tag)</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Usage restreint (étiquette jaune)</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Uso restringido (etiqueta amarilla)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Building has identified hazards that restrict occupancy to specific areas or conditions; detailed evaluation required before full reoccupation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>unsafe</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Unsafe (red tag)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Dangereux (étiquette rouge)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Inseguro (etiqueta roja)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Building poses imminent risk of collapse or is otherwise unsafe to occupy; entry is prohibited pending engineering intervention.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>tarpaulin</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Tarpaulin</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Bâche</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Lona</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Heavy-duty plastic tarpaulin used for emergency shelter construction or dwelling repair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>plastic_sheeting</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Plastic sheeting</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Feuilles plastiques</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Láminas plásticas</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Reinforced plastic sheeting for roofing, walling, or waterproofing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>rope_fixings</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Rope and fixings</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Corde et fixations</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Cuerda y fijaciones</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Rope, wire, nails, or similar fixings required to erect emergency shelter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>blanket</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Blanket</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Couverture</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Blankets for warmth, typically one per household member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>sleeping_mat</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Sleeping mat</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Natte de couchage</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Estera para dormir</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Sleeping mat or bedding, typically one per household member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>cooking_set</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Cooking set</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Kit de cuisine</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Juego de cocina</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Pots, pans, utensils, and plates for household meal preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>jerrycan</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Water container (jerrycan)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Jerrycan à eau</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Bidón de agua</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Water storage and transport container, typically 10-20 litres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>clothing</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Vêtements</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Ropa</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Culturally appropriate clothing; context-dependent sizing and composition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>solar_lantern</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Solar lantern</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Lanterne solaire</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Lámpara solar</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Solar-powered or battery lantern used for lighting when grid power is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>hygiene_kit</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Hygiene kit</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Kit d'hygiène</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Kit de higiene</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Soap, sanitary items, toothbrush, and related hygiene supplies, composition per Sphere WASH standards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>winterization_kit</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Winterization kit</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Kit d'hivernisation</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Kit de invernación</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Context-specific cold-weather supplies (heaters, insulation, winter clothing, thermal blankets) for cold-climate or high-altitude deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>cooking_pot</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Cooking pot</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Marmite</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Olla</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Large cooking pot with handle and lid for household meal preparation. Used in NFIProfile unmet-needs reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>plate_or_bowl</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Plate or bowl</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Assiette ou bol</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Plato o tazón</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Dished plate or deep bowl for individual meal serving (Sphere Std 2: one per person).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>cup_or_mug</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Cup or mug</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Tasse ou mug</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Taza o jarro</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Drinking vessel (Sphere Std 2: one per person).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>kitchen_knife</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen knife</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Couteau de cuisine</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Cuchillo de cocina</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Knife for food preparation (Sphere Std 2: one per household).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>matches_or_lighter</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Matches or lighter</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Allumettes ou briquet</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Fósforos o encendedor</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Ignition source for cooking stove or fire. UNHCR CRI: listed as a renewable NFI requiring regular resupply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>mosquito_net</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Mosquito net (ITN/LLIN)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Moustiquaire (MII/MIILDA)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Mosquitero (MTI/MILD)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Insecticide-treated mosquito net for sleeping protection. Sphere Std 1 key indicator in malaria-endemic settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>clothing_adult</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Clothing (adult)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Vêtements (adulte)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Ropa (adulto)</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Climate-appropriate clothing set for adult household members. Sphere Std 1: two full sets per person in the correct size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>clothing_child</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Clothing (child)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Vêtements (enfant)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Ropa (niño)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Climate-appropriate clothing set for child household members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>shelter_repair_tools</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Shelter repair tools</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Outils de réparation d'abri</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Herramientas de reparación de refugio</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Hammer, nails, rope or equivalent shelter maintenance kit (Sphere Std 4 tools and equipment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>water_jerrycan</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Water jerry can</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Jerrican à eau</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Bidón para agua</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Lidded water transport and storage container (10-20 litre). Overlaps with the generic jerrycan code; water_jerrycan is used in NFIProfile unmet-needs reporting when the specific use case is water-carrying rather than fuel storage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Other essential NFI not captured by the standard categories; narrative description expected at the record level.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>repair_in_place</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Repair in place</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Réparer sur place</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Reparar en el mismo sitio</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Household intends to repair the damaged dwelling at its current location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>rebuild_in_place</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Rebuild in place</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Reconstruire sur place</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Reconstruir en el mismo sitio</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Household intends to demolish the damaged dwelling and rebuild a new dwelling at the same location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>relocate</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Relocate to a different site</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Se relocaliser sur un autre site</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Relocalizarse a otro sitio</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Household intends to move to a different location rather than repair or rebuild at the damaged site (for example, because the site is flood-prone or no longer accessible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>cannot_act_without_support</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Cannot act without external support</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Ne peut agir sans soutien extérieur</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>No puede actuar sin apoyo externo</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Household has no plan to repair, rebuild, or relocate because it lacks the resources to do so without external assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>undecided</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Undecided</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Indécis</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Indeciso</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Household has not yet decided how to respond to the damage.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Eau</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Drinking-water supply is not functioning or not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>sanitation</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Sanitation</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Assainissement</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Saneamiento</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Sanitation facility (toilet, latrine, greywater disposal) is damaged or unusable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Électricité</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Grid or off-grid electricity supply is not functioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>telecommunications</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Télécommunications</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Mobile or fixed-line telecommunications (voice, SMS, data) are not functioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>water_unsafe</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Water present but unsafe</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Eau disponible mais non potable</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Agua disponible pero no apta</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Drinking-water supply is physically available but contaminated or otherwise not safe to drink without further treatment (for example, visibly turbid, microbiologically unsafe, or mixed with sewage). Use alongside the water code when both outage and safety issues are relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>water_intermittent</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Water intermittent</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Eau intermittente</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Agua intermitente</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Drinking-water supply is functioning only part of the time (scheduled rationing, pressure drops, or unreliable source), such that household access is not continuous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>electricity_intermittent</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Electricity intermittent</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Électricité intermittente</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Electricidad intermitente</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Grid or off-grid electricity supply is functioning only part of the time (scheduled load shedding, partial-day outages, unreliable source), such that continuous household use is not possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>sanitation_overflowing</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Sanitation overflowing or unsanitary</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Assainissement débordant ou insalubre</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Saneamiento desbordado o insalubre</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Sanitation facility is physically present but overflowing, flooded, or otherwise in an unsanitary state that makes safe use impossible (e.g., a pit latrine inundated after flooding). Use alongside the sanitation code when both full breakdown and unsanitary state are relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>No service disruption</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Aucune interruption de service</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Sin interrupción de servicio</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Recorded explicitly to distinguish from missing observation when the household reports that all services are currently functioning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2030,12 +4393,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2070,135 +4433,108 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>destroyed</t>
+          <t>self</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Destroyed</t>
+          <t>Self-report</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Détruit</t>
+          <t>Auto-déclaration</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Destruido</t>
+          <t>Autoinforme</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>The structure is completely destroyed or collapsed; rebuilding from foundation is required. Not habitable under any condition.</t>
+          <t>The subject answered the items about themselves. Preferred mode for WG-SS and WG-ES.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>severely_damaged</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Severely damaged</t>
+          <t>Proxy-report</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Gravement endommagé</t>
+          <t>Déclaration par procuration</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Gravemente dañado</t>
+          <t>Informe por terceros</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Major structural damage to load-bearing elements (walls, roof, foundation) rendering the dwelling unsafe. Extensive reconstruction is required before safe occupancy.</t>
+          <t>Another person (caregiver, parent, spouse, household member) answered the items about the subject. Always the mode for the UNICEF Child Functioning Module, because the child is not the respondent.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>moderately_damaged</t>
+          <t>assisted</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Moderately damaged</t>
+          <t>Assisted</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Modérément endommagé</t>
+          <t>Assisté</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Moderadamente dañado</t>
+          <t>Asistido</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Significant damage to non-structural elements (walls, openings, partitions) or limited structural damage. Major repairs are required; dwelling may be temporarily uninhabitable.</t>
+          <t>The subject answered the items but received help from another person (for reading, translation, or comprehension). Distinct from proxy: the subject is still the respondent.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>minor_damage</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Minor damage</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Dommages mineurs</t>
+          <t>Mixte</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Daños menores</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Minor cosmetic or surface damage (cracks, finishes, fixtures). Dwelling remains habitable; minor household-level repairs are sufficient.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>undamaged</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Undamaged</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Non endommagé</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Sin daños</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>No observable damage from the shock. Recorded to distinguish from missing observation.</t>
+          <t>Some items were answered by the subject and others by a proxy. Use when the administration crossed modes within one session, for example because the subject tired or could not answer certain items.</t>
         </is>
       </c>
     </row>
@@ -2213,13 +4549,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2253,135 +4589,405 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>habitable</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>Spouse</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>Conjoint(e)</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Habitable</t>
+          <t>Cónyuge</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Dwelling is currently occupied or occupiable without intervention. No shelter programming action required from a habitability standpoint.</t>
+          <t>A person's husband, wife, or legally recognized partner.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>needs_minor_repairs</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Habitable with minor repairs</t>
+          <t>Parent</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Habitable avec réparations mineures</t>
+          <t>Parent</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Habitable con reparaciones menores</t>
+          <t>Padre/Madre</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Dwelling is livable now; minor household-level repairs (patching, finishes, replacing fixtures) would restore normal function. Typical response: NFI kit or small cash grant.</t>
+          <t>A biological or legally recognized mother or father.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>needs_major_repairs_uninhabitable</t>
+          <t>child</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Uninhabitable; major repairs required (repair-grant tier)</t>
+          <t>Child</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Inhabitable ; réparations majeures requises (tranche subvention-réparation)</t>
+          <t>Enfant</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Inhabitable; se requieren reparaciones mayores (tramo subvención-reparación)</t>
+          <t>Hijo/a</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Dwelling cannot currently be occupied but can be repaired to a safe habitable standard without full reconstruction. Typical response: shelter repair grant, technical assistance, labour support.</t>
+          <t>A biological or legally recognized son or daughter.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>must_be_demolished</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Beyond repair; must be demolished (reconstruction-grant tier)</t>
+          <t>Sibling</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Irréparable ; doit être démoli (tranche subvention-reconstruction)</t>
+          <t>Frère/Sœur</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Irreparable; debe demolerse (tramo subvención-reconstrucción)</t>
+          <t>Hermano/a</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Dwelling is beyond safe repair and must be demolished; recovery requires full reconstruction. Typical response: transitional shelter, reconstruction grant, relocation support.</t>
+          <t>A brother or sister sharing at least one biological or legal parent.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>grandparent</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Unknown / not assessed</t>
+          <t>Grandparent</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Inconnu / non évalué</t>
+          <t>Grand-parent</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Desconocido / no evaluado</t>
+          <t>Abuelo/a</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Habitability has not been assessed. Recorded to distinguish from a positive 'habitable' finding.</t>
+          <t>A parent of a person's parent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>grandchild</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Grandchild</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Petit-enfant</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Nieto/a</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>A child of a person's child.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Tuteur/Tutrice</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Tutor/a</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>A person with legal responsibility for the care and management of another, typically a minor or incapacitated adult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>caregiver</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Caregiver</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Soignant(e)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Cuidador/a</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>A person who provides ongoing care or assistance, whether or not they hold legal guardianship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>dependent</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Personne à charge</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>A person who relies on another for financial support or daily living needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>in_law</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>In-law</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Par alliance</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Pariente político</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>A person related through marriage rather than by blood, such as a parent-in-law, child-in-law, or sibling-in-law.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>extended_family</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Extended family</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Famille élargie</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Familia extendida</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>A family member beyond the immediate kinship categories (e.g. aunt, uncle, cousin, niece, nephew) where the specific type is not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>payment_proxy</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Payment proxy</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Mandataire de paiement</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Apoderado de pago</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>A person authorized to collect benefits on behalf of another, often used when the beneficiary cannot collect in person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>survivor</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Survivor</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Survivant(e)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Sobreviviente</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>A person entitled to continued or transferred benefits following the death of the primary beneficiary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>non_relative</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Non-relative</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Non-parent</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>No pariente</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>A person known to the household or group who has no kinship or legal tie to the reference person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>A relationship type not covered by the other categories.</t>
         </is>
       </c>
     </row>
@@ -2396,13 +5002,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2436,297 +5042,162 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>original_home</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Original home</t>
+          <t>Permanent structure</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Logement d'origine</t>
+          <t>Construction permanente</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Vivienda original</t>
+          <t>Estructura permanente</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Household remains in its usual dwelling.</t>
+          <t>Built with durable materials such as concrete, brick, stone, or metal framing, expected to last 20 or more years.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>original_home_repaired</t>
+          <t>semi_permanent</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Original home, partially repaired</t>
+          <t>Semi-permanent structure</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Logement d'origine, partiellement réparé</t>
+          <t>Construction semi-permanente</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Vivienda original, parcialmente reparada</t>
+          <t>Estructura semipermanente</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Household is back in its usual dwelling after undertaking partial repairs.</t>
+          <t>Mix of durable and non-durable materials, such as mud walls with a metal roof.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>tent_or_emergency_shelter</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Tent or emergency shelter</t>
+          <t>Temporary structure</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Tente ou abri d'urgence</t>
+          <t>Construction temporaire</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Tienda o refugio de emergencia</t>
+          <t>Estructura temporal</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Household is living in an emergency tent, plastic-sheeting shelter, or similar emergency structure.</t>
+          <t>Built with non-durable materials such as thatch, bamboo, or unfired mud.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>transitional_shelter</t>
+          <t>improvised</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Transitional shelter</t>
+          <t>Improvised dwelling</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Abri transitionnel</t>
+          <t>Logement de fortune</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Refugio transicional</t>
+          <t>Vivienda improvisada</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Household is living in a transitional shelter unit provided by a humanitarian agency or government, intended as a bridge to permanent reconstruction.</t>
+          <t>Makeshift shelter made from waste materials, plastic sheeting, or scrap; includes shacks in informal settlements.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>collective_center</t>
+          <t>collective</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Collective centre</t>
+          <t>Collective living quarters</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Centre collectif</t>
+          <t>Logement collectif</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Centro colectivo</t>
+          <t>Vivienda colectiva</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Household is sheltering in a collective centre such as a school, public hall, or place of worship being used as temporary accommodation.</t>
+          <t>Dormitories, barracks, institutions, refugee camps, or hotels used as long-term housing.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>host_family</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Hosted by another family</t>
+          <t>Mobile housing unit</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Hébergé par une autre famille</t>
+          <t>Logement mobile</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Alojado por otra familia</t>
+          <t>Vivienda móvil</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Household is staying with a host family (relatives, friends, or other hosts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>rented_accommodation</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Rented accommodation</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Logement loué</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Alojamiento alquilado</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Household has rented a separate dwelling as temporary or continuing accommodation after the shock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>displacement_site</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Displacement site or camp</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Site de déplacement ou camp</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Sitio de desplazamiento o campamento</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Household is in a managed displacement site or camp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>unsheltered</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Unsheltered / open air</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Sans abri / à l'air libre</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Sin refugio / a la intemperie</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Household is without shelter (sleeping outside, under tarpaulin strung between trees, or in vehicles).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>camp_planned</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Planned or managed camp</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Camp planifié ou géré</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Campamento planificado o gestionado</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Household is living in an official displacement camp or settlement managed by a government, UN agency, or NGO with designated administration. Equivalent to IOM DTM site classification 'planned/managed camp'. Distinct from spontaneous_settlement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>spontaneous_settlement</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Spontaneous or informal settlement</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Établissement spontané ou informel</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Asentamiento espontáneo o informal</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Household is living in an unplanned settlement that emerged organically, often on public or private land without official sanction or management. Equivalent to IOM DTM site classification 'informal/spontaneous settlement'.</t>
+          <t>Tents, caravans, houseboats, or other movable structures used as a primary residence.</t>
         </is>
       </c>
     </row>
@@ -2741,13 +5212,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2781,81 +5252,270 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>safe</t>
+          <t>earth_sand</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Safe (green tag)</t>
+          <t>Earth or sand</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sûr (étiquette verte)</t>
+          <t>Terre ou sable</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Seguro (etiqueta verde)</t>
+          <t>Tierra o arena</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Building is structurally safe to occupy; no restrictions identified.</t>
+          <t>Unpaved floor made of bare earth or sand.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>restricted_use</t>
+          <t>dung</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Restricted use (yellow tag)</t>
+          <t>Dung</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Usage restreint (étiquette jaune)</t>
+          <t>Bouse</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Uso restringido (etiqueta amarilla)</t>
+          <t>Estiércol</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Building has identified hazards that restrict occupancy to specific areas or conditions; detailed evaluation required before full reoccupation.</t>
+          <t>Floor finished with dung, a traditional material used in parts of sub-Saharan Africa and South Asia.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>unsafe</t>
+          <t>wood_planks</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Unsafe (red tag)</t>
+          <t>Wood planks</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Dangereux (étiquette rouge)</t>
+          <t>Planches de bois</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Inseguro (etiqueta roja)</t>
+          <t>Tablones de madera</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Building poses imminent risk of collapse or is otherwise unsafe to occupy; entry is prohibited pending engineering intervention.</t>
+          <t>Floor made of unpolished wood planks or boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>palm_bamboo</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Palm or bamboo</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Palme ou bambou</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Palma o bambú</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Floor made of woven or split palm fronds or bamboo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>parquet_polished_wood</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Parquet or polished wood</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Parquet ou bois poli</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Parquet o madera pulida</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Floor made of finished hardwood, parquet blocks, or polished wood boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>vinyl_asphalt</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Vinyl or asphalt strips</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Vinyle ou dalles en asphalte</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Vinilo o tiras de asfalto</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Floor covered with vinyl tiles, linoleum, or asphalt strips.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>ceramic_tiles</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic tiles</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Carreaux céramique</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Baldosas cerámicas</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Floor covered with ceramic, porcelain, or similar fired clay tiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Ciment</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Cemento</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Floor made of poured or troweled cement or concrete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>carpet</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Carpet</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Moquette</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Alfombra</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Floor covered with carpet or fitted rugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Floor material not covered by the other categories.</t>
         </is>
       </c>
     </row>
@@ -2870,13 +5530,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2910,594 +5570,432 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>tarpaulin</t>
+          <t>no_walls</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Tarpaulin</t>
+          <t>No walls</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Bâche</t>
+          <t>Sans murs</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Lona</t>
+          <t>Sin paredes</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Heavy-duty plastic tarpaulin used for emergency shelter construction or dwelling repair.</t>
+          <t>Dwelling has no exterior walls (open structure).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>plastic_sheeting</t>
+          <t>cane_palm_trunks</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Plastic sheeting</t>
+          <t>Cane, palm, or trunks</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Feuilles plastiques</t>
+          <t>Cannes, palmes ou troncs</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Láminas plásticas</t>
+          <t>Caña, palma o troncos</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Reinforced plastic sheeting for roofing, walling, or waterproofing.</t>
+          <t>Walls made of natural cane, palm fronds, or tree trunks without additional finishing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>rope_fixings</t>
+          <t>dirt</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Rope and fixings</t>
+          <t>Dirt</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Corde et fixations</t>
+          <t>Terre</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Cuerda y fijaciones</t>
+          <t>Tierra</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Rope, wire, nails, or similar fixings required to erect emergency shelter.</t>
+          <t>Walls made of packed dirt or mud without any structural reinforcement.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>blanket</t>
+          <t>bamboo_with_mud</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Blanket</t>
+          <t>Bamboo with mud</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Couverture</t>
+          <t>Bambou avec boue</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Bambú con barro</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Blankets for warmth, typically one per household member.</t>
+          <t>Bamboo frame walls plastered or filled with mud.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>sleeping_mat</t>
+          <t>stone_with_mud</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sleeping mat</t>
+          <t>Stone with mud</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Natte de couchage</t>
+          <t>Pierre avec boue</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Estera para dormir</t>
+          <t>Piedra con barro</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Sleeping mat or bedding, typically one per household member.</t>
+          <t>Stone walls bonded with mud rather than mortar or cement.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>cooking_set</t>
+          <t>uncovered_adobe</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Cooking set</t>
+          <t>Uncovered adobe</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Kit de cuisine</t>
+          <t>Adobe non revêtu</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Juego de cocina</t>
+          <t>Adobe sin revestir</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Pots, pans, utensils, and plates for household meal preparation.</t>
+          <t>Sun-dried mud brick (adobe) walls without an exterior plaster or render coating.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>jerrycan</t>
+          <t>plywood</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Water container (jerrycan)</t>
+          <t>Plywood</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Jerrycan à eau</t>
+          <t>Contreplaqué</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Bidón de agua</t>
+          <t>Contrachapado</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Water storage and transport container, typically 10-20 litres.</t>
+          <t>Walls made of plywood sheets.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>clothing</t>
+          <t>cardboard</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Vêtements</t>
+          <t>Carton</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Ropa</t>
+          <t>Cartón</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Culturally appropriate clothing; context-dependent sizing and composition.</t>
+          <t>Walls made of cardboard or similar paper-based material.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>solar_lantern</t>
+          <t>reused_wood</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Solar lantern</t>
+          <t>Reused wood</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Lanterne solaire</t>
+          <t>Bois récupéré</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Lámpara solar</t>
+          <t>Madera reutilizada</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Solar-powered or battery lantern used for lighting when grid power is unavailable.</t>
+          <t>Walls built from salvaged or reused wooden boards and planks.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>hygiene_kit</t>
+          <t>cement</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Hygiene kit</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Kit d'hygiène</t>
+          <t>Ciment</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Kit de higiene</t>
+          <t>Cemento</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Soap, sanitary items, toothbrush, and related hygiene supplies, composition per Sphere WASH standards.</t>
+          <t>Walls made of poured concrete or cement render on a structural frame.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>winterization_kit</t>
+          <t>stone_with_lime_cement</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Winterization kit</t>
+          <t>Stone with lime or cement</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Kit d'hivernisation</t>
+          <t>Pierre avec chaux ou ciment</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Kit de invernación</t>
+          <t>Piedra con cal o cemento</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Context-specific cold-weather supplies (heaters, insulation, winter clothing, thermal blankets) for cold-climate or high-altitude deployments.</t>
+          <t>Stone walls bonded with lime or cement mortar.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>cooking_pot</t>
+          <t>bricks</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Cooking pot</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Marmite</t>
+          <t>Briques</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Olla</t>
+          <t>Ladrillos</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Large cooking pot with handle and lid for household meal preparation. Used in NFIProfile unmet-needs reporting.</t>
+          <t>Walls made of fired clay bricks.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>plate_or_bowl</t>
+          <t>cement_blocks</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Plate or bowl</t>
+          <t>Cement blocks</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Assiette ou bol</t>
+          <t>Parpaings</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Plato o tazón</t>
+          <t>Bloques de cemento</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Dished plate or deep bowl for individual meal serving (Sphere Std 2: one per person).</t>
+          <t>Walls made of concrete masonry units (hollow or solid cement blocks).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>cup_or_mug</t>
+          <t>covered_adobe</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Cup or mug</t>
+          <t>Covered adobe</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Tasse ou mug</t>
+          <t>Adobe revêtu</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Taza o jarro</t>
+          <t>Adobe revestido</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Drinking vessel (Sphere Std 2: one per person).</t>
+          <t>Adobe (sun-dried mud brick) walls with an exterior plaster or render coating.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>kitchen_knife</t>
+          <t>wood_planks_shingles</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Kitchen knife</t>
+          <t>Wood planks or shingles</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Couteau de cuisine</t>
+          <t>Planches ou bardeaux de bois</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Cuchillo de cocina</t>
+          <t>Tablones o tejas de madera</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Knife for food preparation (Sphere Std 2: one per household).</t>
+          <t>Walls clad with milled wood planks or wooden shingles.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>matches_or_lighter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Matches or lighter</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Allumettes ou briquet</t>
+          <t>Autre</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Fósforos o encendedor</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Ignition source for cooking stove or fire. UNHCR CRI: listed as a renewable NFI requiring regular resupply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>mosquito_net</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Mosquito net (ITN/LLIN)</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Moustiquaire (MII/MIILDA)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Mosquitero (MTI/MILD)</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Insecticide-treated mosquito net for sleeping protection. Sphere Std 1 key indicator in malaria-endemic settings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>clothing_adult</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Clothing (adult)</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Vêtements (adulte)</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Ropa (adulto)</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Climate-appropriate clothing set for adult household members. Sphere Std 1: two full sets per person in the correct size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>clothing_child</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Clothing (child)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Vêtements (enfant)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Ropa (niño)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Climate-appropriate clothing set for child household members.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>shelter_repair_tools</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Shelter repair tools</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Outils de réparation d'abri</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Herramientas de reparación de refugio</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Hammer, nails, rope or equivalent shelter maintenance kit (Sphere Std 4 tools and equipment).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>water_jerrycan</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Water jerry can</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Jerrican à eau</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Bidón para agua</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Lidded water transport and storage container (10-20 litre). Overlaps with the generic jerrycan code; water_jerrycan is used in NFIProfile unmet-needs reporting when the specific use case is water-carrying rather than fuel storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Autre</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Other essential NFI not captured by the standard categories; narrative description expected at the record level.</t>
+          <t>Wall material not covered by the other categories.</t>
         </is>
       </c>
     </row>
@@ -3512,13 +6010,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3552,135 +6050,378 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>repair_in_place</t>
+          <t>no_roof</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Repair in place</t>
+          <t>No roof</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Réparer sur place</t>
+          <t>Sans toit</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Reparar en el mismo sitio</t>
+          <t>Sin techo</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Household intends to repair the damaged dwelling at its current location.</t>
+          <t>Dwelling has no roof covering.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>rebuild_in_place</t>
+          <t>thatch_palm_leaf</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Rebuild in place</t>
+          <t>Thatch or palm leaf</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Reconstruire sur place</t>
+          <t>Chaume ou feuille de palme</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Reconstruir en el mismo sitio</t>
+          <t>Paja o hoja de palma</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Household intends to demolish the damaged dwelling and rebuild a new dwelling at the same location.</t>
+          <t>Roof made of dried grass, straw, reeds, or palm leaves bundled into thatch.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>relocate</t>
+          <t>sod_grass</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Relocate to a different site</t>
+          <t>Sod or grass</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Se relocaliser sur un autre site</t>
+          <t>Gazon ou herbe</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Relocalizarse a otro sitio</t>
+          <t>Césped o hierba</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Household intends to move to a different location rather than repair or rebuild at the damaged site (for example, because the site is flood-prone or no longer accessible).</t>
+          <t>Roof covered with living or dried sod, turf, or loose grass.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>cannot_act_without_support</t>
+          <t>rustic_mat</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Cannot act without external support</t>
+          <t>Rustic mat</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Ne peut agir sans soutien extérieur</t>
+          <t>Natte rudimentaire</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>No puede actuar sin apoyo externo</t>
+          <t>Estera rústica</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Household has no plan to repair, rebuild, or relocate because it lacks the resources to do so without external assistance.</t>
+          <t>Roof covered with woven plant-fiber mats (e.g., reed or rush mats).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>palm_bamboo</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Undecided</t>
+          <t>Palm or bamboo</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Indécis</t>
+          <t>Palme ou bambou</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Indeciso</t>
+          <t>Palma o bambú</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Household has not yet decided how to respond to the damage.</t>
+          <t>Roof structure made of palm fronds or split bamboo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>wood_planks</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Wood planks</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Planches de bois</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Tablones de madera</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Roof made of unfinished wood planks or boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>cardboard</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Cardboard</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Carton</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Cartón</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Roof covered with cardboard or similar paper-based material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>metal</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Metal or tin sheets</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Tôle métallique</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Láminas metálicas</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Roof made of corrugated iron, galvanized steel, aluminum, or other metal sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Bois</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Madera</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Roof made of finished or milled wooden boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>calamine_cement_fiber</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Calamine or cement fiber</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Calamine ou fibrociment</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Calamina o fibrocemento</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Roof made of corrugated calamine sheeting or fiber-cement (e.g., Eternit) panels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>ceramic_tiles</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Ceramic tiles</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Tuiles céramiques</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Tejas cerámicas</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Roof covered with fired clay or ceramic tiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Ciment</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Cemento</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Flat or sloped roof made of poured concrete or reinforced cement slab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>roofing_shingles</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Roofing shingles</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Bardeaux de toiture</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Tejas de pizarra</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Roof covered with asphalt, fiberglass, or wooden shingles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Roof material not covered by the other categories.</t>
         </is>
       </c>
     </row>
@@ -3695,13 +6436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3735,243 +6476,432 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>piped_into_dwelling</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Piped into dwelling</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Eau courante dans le logement</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Agua</t>
+          <t>Agua por tubería en la vivienda</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Drinking-water supply is not functioning or not available.</t>
+          <t>Water piped directly into the dwelling, yard, or plot through a household connection.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>sanitation</t>
+          <t>piped_to_yard</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Sanitation</t>
+          <t>Piped to yard/plot</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Assainissement</t>
+          <t>Eau courante dans la cour/parcelle</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Saneamiento</t>
+          <t>Agua por tubería en el patio/parcela</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Sanitation facility (toilet, latrine, greywater disposal) is damaged or unusable.</t>
+          <t>Water piped to the yard or plot outside the dwelling but within the household's controlled space.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>piped_to_neighbor</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Piped to neighbor</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Électricité</t>
+          <t>Eau courante chez un voisin</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Agua por tubería en casa del vecino</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Grid or off-grid electricity supply is not functioning.</t>
+          <t>Water obtained from a neighbor's piped household connection.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>telecommunications</t>
+          <t>public_tap_standpipe</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Public tap/standpipe</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Télécommunications</t>
+          <t>Robinet public/borne-fontaine</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Telecomunicaciones</t>
+          <t>Grifo público/surtidor</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Mobile or fixed-line telecommunications (voice, SMS, data) are not functioning.</t>
+          <t>A communal tap or standpipe that supplies water to multiple households in a public area.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>water_unsafe</t>
+          <t>tube_well_borehole</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Water present but unsafe</t>
+          <t>Tube well or borehole</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Eau disponible mais non potable</t>
+          <t>Puits tubulaire ou forage</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Agua disponible pero no apta</t>
+          <t>Pozo entubado o perforación</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Drinking-water supply is physically available but contaminated or otherwise not safe to drink without further treatment (for example, visibly turbid, microbiologically unsafe, or mixed with sewage). Use alongside the water code when both outage and safety issues are relevant.</t>
+          <t>A narrow-diameter well drilled into the ground and fitted with a hand pump or motorized pump to extract groundwater.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>water_intermittent</t>
+          <t>protected_well</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Water intermittent</t>
+          <t>Protected dug well</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Eau intermittente</t>
+          <t>Puits creusé protégé</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Agua intermitente</t>
+          <t>Pozo excavado protegido</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Drinking-water supply is functioning only part of the time (scheduled rationing, pressure drops, or unreliable source), such that household access is not continuous.</t>
+          <t>A dug well protected from runoff and surface contamination by a lining, cover, and apron.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>electricity_intermittent</t>
+          <t>unprotected_well</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Electricity intermittent</t>
+          <t>Unprotected dug well</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Électricité intermittente</t>
+          <t>Puits creusé non protégé</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Electricidad intermitente</t>
+          <t>Pozo excavado sin protección</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Grid or off-grid electricity supply is functioning only part of the time (scheduled load shedding, partial-day outages, unreliable source), such that continuous household use is not possible.</t>
+          <t>A dug well without a protective lining or cover, exposed to potential surface contamination.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>sanitation_overflowing</t>
+          <t>protected_spring</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Sanitation overflowing or unsanitary</t>
+          <t>Protected spring</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Assainissement débordant ou insalubre</t>
+          <t>Source protégée</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Saneamiento desbordado o insalubre</t>
+          <t>Manantial protegido</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sanitation facility is physically present but overflowing, flooded, or otherwise in an unsanitary state that makes safe use impossible (e.g., a pit latrine inundated after flooding). Use alongside the sanitation code when both full breakdown and unsanitary state are relevant.</t>
+          <t>A natural spring protected from runoff and surface contamination by a spring box or similar structure.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>unprotected_spring</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>No service disruption</t>
+          <t>Unprotected spring</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Aucune interruption de service</t>
+          <t>Source non protégée</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Sin interrupción de servicio</t>
+          <t>Manantial sin protección</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Recorded explicitly to distinguish from missing observation when the household reports that all services are currently functioning.</t>
+          <t>A natural spring without any protection structure, exposed to potential surface contamination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>rainwater</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Rainwater collection</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Collecte d'eau de pluie</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Recolección de agua de lluvia</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Water collected from rooftops or other surfaces and stored in a tank or container.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>tanker_truck</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Tanker truck</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Camion-citerne</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Camión cisterna</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Water delivered by a motorized tanker truck or tanker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>cart_with_small_tank</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Cart with small tank/drum</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Charrette avec petit réservoir/bidon</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Carreta con depósito pequeño/bidón</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Water delivered by a cart, donkey, or other non-motorized transport carrying a small tank or drum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>surface_water</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Surface water</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Eau de surface</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Agua superficial</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Water drawn directly from a river, dam, lake, pond, stream, canal, or irrigation channel without any treatment or protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>bottled_water</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Bottled water</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Eau en bouteille</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Agua embotellada</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Commercially packaged water sold in sealed bottles, typically treated or purified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>packaged_water</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Sachet/packaged water</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Eau en sachet/conditionnée</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Agua en bolsa/envasada</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Commercially packaged water sold in sealed sachets or other small disposable containers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>A drinking water source not covered by the other categories.</t>
         </is>
       </c>
     </row>
